--- a/第11组_填表内容_可粘贴.xlsx
+++ b/第11组_填表内容_可粘贴.xlsx
@@ -713,10 +713,14 @@
       <c r="X2" s="2" t="n"/>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>整体验收：贯通 7 项加分功能的完整演示路径；整理提交包与部署说明；组织代码评审与答辩彩排；补齐 README、ER 图与操作手册（仓库当前 0 个 .md 文件）。</t>
-        </is>
-      </c>
-      <c r="Z2" s="2" t="n"/>
+          <t>交付包整理与答辩准备：按课程模板八节重写 README，整理 src／config／data／evidence 四个目录，config 只放占位符模板；补齐 evidence 的构建与自动化测试记录、关键接口返回；提交前做安全核验，剔除真实密钥与人脸特征、账号记录、简历、报告等运行期隐私数据；组织现场验收流程彩排与三人分工讲解。</t>
+        </is>
+      </c>
+      <c r="Z2" s="2" t="inlineStr">
+        <is>
+          <t>交付包整理完成：README 按模板八节写定；src 收入 Spring Boot 后端、Vue3 用户端与管理端、Python AI 能力服务三份源码，并与源目录逐文件核对一致；config 提供 .env.example、application-local.yml.example 与配置说明，全部使用占位符；evidence 收入构建与自动化测试记录及关键接口返回；安全核验中查出并剔除误打包的人脸特征文件、账号记录、简历原文与演示数据库文件，最终包体 6 MB，真实密钥扫描无命中。验收流程彩排完成。</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="260" customHeight="1">
       <c r="A3" s="2" t="n"/>
@@ -813,10 +817,14 @@
       <c r="X3" s="2" t="n"/>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>AI 链路异常测试：无摄像头、无麦克风、Python 服务不可用与超时场景下的降级验证；修复并验证音频分片序号并发撞唯一键（现用 count()+1）；补齐 interview_transcript.segments_json 落库与 ASR 失败重试；输出 ASR／TTS／视觉接口参数说明。</t>
-        </is>
-      </c>
-      <c r="Z3" s="2" t="n"/>
+          <t>AI 链路验收与降级验证：用新的文本回答与合成面试人像分别验证两个感知模块处理新输入并返回真实结果；验证未采集视觉样本时报告各维度显示「未评估」且不出综合分；核验融合公式与报告中的输入追溯；排查 Java 侧读超时与 Python 侧大模型超时不一致导致的提前超时隐患；输出 AI 服务接口与参数说明。</t>
+        </is>
+      </c>
+      <c r="Z3" s="2" t="inlineStr">
+        <is>
+          <t>两个感知模块验收通过：新的文本回答经大模型逐题评测返回真实问答得分，合成面试人像逐帧送入后 MediaPipe 采集到 50 帧人脸并输出表情与注意力分；融合结果核验为 45.0×0.8＋65.0×0.2＝49.0，与报告公式一致；未采集视觉样本时报告各维度显示「未评估」且综合分为空。查出 Java 侧读超时 60 秒小于 Python 侧大模型超时 90 秒，存在 Java 先超时的隐患，已登记并给出调整建议；AI 服务接口与参数说明补充完成。</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="260" customHeight="1">
       <c r="A4" s="2" t="n"/>
@@ -913,10 +921,14 @@
       <c r="X4" s="2" t="n"/>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>系统测试与交付：补齐业务单元测试（现存 5 个测试类全是空的 contextLoads、零断言），编写并执行测试用例，输出测试报告与缺陷清单；完成管理端页面联调收尾。</t>
-        </is>
-      </c>
-      <c r="Z4" s="2" t="n"/>
+          <t>系统测试与交付收尾：清理原有的空壳测试类，补齐可执行的业务单元测试；编写正常、异常、权限三类测试用例并执行，输出测试结果表；完成管理端页面联调收尾；输出缺陷清单与项目风险表。</t>
+        </is>
+      </c>
+      <c r="Z4" s="2" t="inlineStr">
+        <is>
+          <t>系统测试完成：删除原有的空壳 contextLoads 测试类，新增权限契约测试与验收回归测试共 9 个用例，覆盖状态流转、越权访问、报告融合与未测维度处理，全部通过；配合冒烟脚本执行正常、异常、权限三类现场用例共 22 项，全部通过，并据此输出测试结果表；管理端页面联调收尾完成，输出缺陷清单与项目风险表。</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
